--- a/competitor-analysis/competitor_scorecard.xlsx
+++ b/competitor-analysis/competitor_scorecard.xlsx
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ACQUIRED by Arcium (Nov 2024); winding down</t>
+          <t>Core tech &amp; team acquired by Arcium (Nov 2024); winding down</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Public (CFLT); NB: IBM acquiring (~$11B, Mar 2026); 800 layoffs Mar 2026</t>
+          <t>Public (CFLT); IBM acquisition COMPLETED ~$11B, 17 Mar 2026 (announced Dec 2025)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3588,7 +3588,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Method: 48 competitors across 12 categories were analysed on website positioning (CTAs, keywords,</t>
+          <t>Method: 47 competitors across 19 category labels were analysed on website positioning (CTAs, keywords,</t>
         </is>
       </c>
     </row>

--- a/competitor-analysis/competitor_scorecard.xlsx
+++ b/competitor-analysis/competitor_scorecard.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>~24,800</t>
+          <t>~22,000</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
